--- a/data_out/nuts3_stats_by_country/LT.xlsx
+++ b/data_out/nuts3_stats_by_country/LT.xlsx
@@ -431,12 +431,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NUTS_ID</t>
+          <t>nuts_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>NUTS_NAME</t>
+          <t>nuts_name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>NAME_LATN</t>
+          <t>name_latn</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
